--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484666_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484666_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.5528</v>
+        <v>7.3578</v>
       </c>
       <c r="E2" t="n">
-        <v>7.9993</v>
+        <v>5.9529</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5536</v>
+        <v>1.4049</v>
       </c>
       <c r="G2" t="n">
         <v>5.6399</v>
@@ -610,13 +610,13 @@
         <v>2.1991</v>
       </c>
       <c r="S2" t="n">
-        <v>4.7742</v>
+        <v>2.5792</v>
       </c>
       <c r="T2" t="n">
-        <v>3.7527</v>
+        <v>1.7063</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0215</v>
+        <v>0.8729</v>
       </c>
       <c r="V2" t="n">
         <v>-0.3115</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.8852</v>
+        <v>4.1757</v>
       </c>
       <c r="E3" t="n">
-        <v>5.2944</v>
+        <v>5.13</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.4093</v>
+        <v>-0.9543</v>
       </c>
       <c r="G3" t="n">
         <v>2.784</v>
@@ -688,13 +688,13 @@
         <v>2.5656</v>
       </c>
       <c r="S3" t="n">
-        <v>3.2294</v>
+        <v>2.52</v>
       </c>
       <c r="T3" t="n">
-        <v>1.4261</v>
+        <v>1.2617</v>
       </c>
       <c r="U3" t="n">
-        <v>1.8033</v>
+        <v>1.2583</v>
       </c>
       <c r="V3" t="n">
         <v>-0.945</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>K. MONTAÑO LINARES</t>
+          <t>B. MONDRAGON VIDAL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,58 +721,58 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5256</v>
+        <v>2.8114</v>
       </c>
       <c r="E4" t="n">
-        <v>2.5256</v>
+        <v>2.0075</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>0.8038999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>2.5256</v>
+        <v>0.7408</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6502</v>
+        <v>1.2405</v>
       </c>
       <c r="I4" t="n">
-        <v>1.8753</v>
+        <v>-0.4998</v>
       </c>
       <c r="J4" t="n">
-        <v>2.5256</v>
+        <v>2.1331</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6502</v>
+        <v>3.3378</v>
       </c>
       <c r="L4" t="n">
-        <v>1.8753</v>
+        <v>-1.2048</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>-1.3923</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>-2.0973</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>0.705</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>0.3665</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.2828</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.7042</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>0.7907</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>0.9134</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B. MONDRAGON VIDAL</t>
+          <t>J. BALLESTER FERRANDIS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3767</v>
+        <v>2.5666</v>
       </c>
       <c r="E5" t="n">
-        <v>1.7462</v>
+        <v>3.0295</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6304999999999999</v>
+        <v>-0.4628</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7408</v>
+        <v>0.185</v>
       </c>
       <c r="H5" t="n">
-        <v>1.2405</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4998</v>
+        <v>-0.747</v>
       </c>
       <c r="J5" t="n">
-        <v>2.1331</v>
+        <v>1.9589</v>
       </c>
       <c r="K5" t="n">
-        <v>3.3378</v>
+        <v>1.8082</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.2048</v>
+        <v>0.1508</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.3923</v>
+        <v>-1.7739</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.0973</v>
+        <v>-0.8762</v>
       </c>
       <c r="O5" t="n">
-        <v>0.705</v>
+        <v>-0.8977000000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3665</v>
+        <v>0.5498</v>
       </c>
       <c r="Q5" t="n">
         <v>-0.9163</v>
       </c>
       <c r="R5" t="n">
-        <v>1.2828</v>
+        <v>1.4661</v>
       </c>
       <c r="S5" t="n">
-        <v>1.2695</v>
+        <v>-0.06859999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5294</v>
+        <v>0.0864</v>
       </c>
       <c r="U5" t="n">
-        <v>0.74</v>
+        <v>-0.155</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.9005</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.9005</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. BALLESTER FERRANDIS</t>
+          <t>M. PANOS HUERTAS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.0745</v>
+        <v>2.5529</v>
       </c>
       <c r="E6" t="n">
-        <v>2.686</v>
+        <v>2.8799</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.6115</v>
+        <v>-0.327</v>
       </c>
       <c r="G6" t="n">
-        <v>0.185</v>
+        <v>1.737</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9320000000000001</v>
+        <v>-1.1741</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.747</v>
+        <v>2.9111</v>
       </c>
       <c r="J6" t="n">
-        <v>1.9589</v>
+        <v>3.4011</v>
       </c>
       <c r="K6" t="n">
-        <v>1.8082</v>
+        <v>0.1051</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1508</v>
+        <v>3.296</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.7739</v>
+        <v>-1.6641</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8762</v>
+        <v>-1.2792</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8977000000000001</v>
+        <v>-0.3849</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5498</v>
+        <v>0.1833</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9163</v>
+        <v>-1.8326</v>
       </c>
       <c r="R6" t="n">
-        <v>1.4661</v>
+        <v>2.0158</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5608</v>
+        <v>1.2556</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2572</v>
+        <v>0.6674</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3036</v>
+        <v>0.5881999999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>1.9005</v>
+        <v>-0.6231</v>
       </c>
       <c r="W6" t="n">
-        <v>1.9005</v>
+        <v>0.6439</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. PANOS HUERTAS</t>
+          <t>K. MONTAÑO LINARES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3821</v>
+        <v>2.5256</v>
       </c>
       <c r="E7" t="n">
-        <v>1.8083</v>
+        <v>2.5256</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4261</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>1.737</v>
+        <v>2.5256</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.1741</v>
+        <v>0.6502</v>
       </c>
       <c r="I7" t="n">
-        <v>2.9111</v>
+        <v>1.8753</v>
       </c>
       <c r="J7" t="n">
-        <v>3.4011</v>
+        <v>2.5256</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1051</v>
+        <v>0.6502</v>
       </c>
       <c r="L7" t="n">
-        <v>3.296</v>
+        <v>1.8753</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.6641</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.2792</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3849</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1833</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.0158</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0849</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4042</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4891</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.6231</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6439</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.267</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. PAÑOS HUERTAS</t>
+          <t>K. MONTANO LINARES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2753</v>
+        <v>1.3584</v>
       </c>
       <c r="E8" t="n">
-        <v>1.2753</v>
+        <v>1.2523</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>0.1061</v>
       </c>
       <c r="G8" t="n">
-        <v>1.2753</v>
+        <v>-2.0273</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6502</v>
+        <v>0.0433</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6251</v>
+        <v>-2.0707</v>
       </c>
       <c r="J8" t="n">
-        <v>1.2753</v>
+        <v>1.2671</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6502</v>
+        <v>2.8886</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6251</v>
+        <v>-1.6215</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>-3.2944</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>-2.8453</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>-0.4492</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.6493</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.5656</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.7364</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>0.891</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>0.8454</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.0104</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.0104</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>K. MONTANO LINARES</t>
+          <t>M. PAÑOS HUERTAS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5524</v>
+        <v>1.2753</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7436</v>
+        <v>1.2753</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1911</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.0273</v>
+        <v>1.2753</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0433</v>
+        <v>0.6502</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.0707</v>
+        <v>0.6251</v>
       </c>
       <c r="J9" t="n">
-        <v>1.2671</v>
+        <v>1.2753</v>
       </c>
       <c r="K9" t="n">
-        <v>2.8886</v>
+        <v>0.6502</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.6215</v>
+        <v>0.6251</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.2944</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.8453</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4492</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.6493</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.5656</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.9305</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3824</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5481</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.0104</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.0104</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4905</v>
+        <v>0.878</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.08840000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5789</v>
+        <v>0.678</v>
       </c>
       <c r="G10" t="n">
         <v>0.5345</v>
@@ -1234,13 +1234,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.044</v>
+        <v>0.3435</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1101</v>
+        <v>0.1784</v>
       </c>
       <c r="U10" t="n">
-        <v>0.06610000000000001</v>
+        <v>0.1652</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.7818000000000001</v>
+        <v>-0.5677</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.4472</v>
+        <v>-1.1587</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6654</v>
+        <v>0.5911</v>
       </c>
       <c r="G11" t="n">
         <v>-0.8974</v>
@@ -1312,13 +1312,13 @@
         <v>0.1833</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.06759999999999999</v>
+        <v>0.1465</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1652</v>
+        <v>0.1233</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0975</v>
+        <v>0.0232</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.919</v>
+        <v>-1.9353</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.2898</v>
+        <v>-0.3309</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.6291</v>
+        <v>-1.6044</v>
       </c>
       <c r="G12" t="n">
         <v>-1.3542</v>
@@ -1390,13 +1390,13 @@
         <v>0.733</v>
       </c>
       <c r="S12" t="n">
-        <v>0.5844</v>
+        <v>0.5681</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3839</v>
+        <v>0.3428</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2005</v>
+        <v>0.2253</v>
       </c>
       <c r="V12" t="n">
         <v>-0.9658</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.5926</v>
+        <v>-4.076</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.8011</v>
+        <v>-3.2103</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.7914</v>
+        <v>-0.8657</v>
       </c>
       <c r="G13" t="n">
         <v>-3.4803</v>
@@ -1468,13 +1468,13 @@
         <v>0.733</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.306</v>
+        <v>0.2106</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6056</v>
+        <v>-0.0147</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2996</v>
+        <v>0.2253</v>
       </c>
       <c r="V13" t="n">
         <v>-0.6231</v>
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>17.8217</v>
+        <v>18.9227</v>
       </c>
       <c r="E14" t="n">
-        <v>18.4522</v>
+        <v>19.5531</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.6301000000000002</v>
+        <v>-0.6302</v>
       </c>
       <c r="G14" t="n">
         <v>7.6629</v>
       </c>
       <c r="H14" t="n">
-        <v>6.059500000000001</v>
+        <v>6.059499999999999</v>
       </c>
       <c r="I14" t="n">
         <v>1.603199999999999</v>
@@ -1525,7 +1525,7 @@
         <v>20.2859</v>
       </c>
       <c r="L14" t="n">
-        <v>1.926</v>
+        <v>1.925999999999999</v>
       </c>
       <c r="M14" t="n">
         <v>-14.549</v>
@@ -1534,7 +1534,7 @@
         <v>-14.2264</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.3226999999999999</v>
+        <v>-0.3227000000000002</v>
       </c>
       <c r="P14" t="n">
         <v>1.8325</v>
@@ -1546,13 +1546,13 @@
         <v>13.7443</v>
       </c>
       <c r="S14" t="n">
-        <v>9.894500000000001</v>
+        <v>10.9955</v>
       </c>
       <c r="T14" t="n">
-        <v>4.9322</v>
+        <v>6.0333</v>
       </c>
       <c r="U14" t="n">
-        <v>4.9621</v>
+        <v>4.9622</v>
       </c>
       <c r="V14" t="n">
         <v>-1.568</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.4432</v>
+        <v>0.7963</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2984</v>
+        <v>-0.2785</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1448</v>
+        <v>1.0748</v>
       </c>
       <c r="G15" t="n">
         <v>0.3838</v>
@@ -1624,13 +1624,13 @@
         <v>1.8326</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1431</v>
+        <v>-0.5038</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6765</v>
+        <v>0.09959999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5334</v>
+        <v>-0.6032999999999999</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0726</v>
+        <v>0.4238</v>
       </c>
       <c r="E16" t="n">
         <v>2.4364</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.3638</v>
+        <v>-2.0126</v>
       </c>
       <c r="G16" t="n">
         <v>-1.1121</v>
@@ -1702,13 +1702,13 @@
         <v>2.1991</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.0248</v>
+        <v>-0.6736</v>
       </c>
       <c r="T16" t="n">
         <v>-0.46</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5648</v>
+        <v>-0.2136</v>
       </c>
       <c r="V16" t="n">
         <v>0.0104</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.14</v>
+        <v>0.0318</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0194</v>
+        <v>0.2117</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1595</v>
+        <v>-0.1799</v>
       </c>
       <c r="G17" t="n">
         <v>1.0186</v>
@@ -1780,13 +1780,13 @@
         <v>0.733</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.3261</v>
+        <v>-1.1542</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8808</v>
+        <v>-0.6885</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4453</v>
+        <v>-0.4657</v>
       </c>
       <c r="V17" t="n">
         <v>1.267</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E. PINA RODRIGUEZ</t>
+          <t>C. HORTELANO ESCRIBA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6844</v>
+        <v>-0.3522</v>
       </c>
       <c r="E18" t="n">
-        <v>1.4823</v>
+        <v>4.0773</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.1667</v>
+        <v>-4.4296</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.0514</v>
+        <v>1.3347</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5672</v>
+        <v>1.1616</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4842</v>
+        <v>0.1731</v>
       </c>
       <c r="J18" t="n">
-        <v>1.2613</v>
+        <v>5.6226</v>
       </c>
       <c r="K18" t="n">
-        <v>1.1363</v>
+        <v>4.9043</v>
       </c>
       <c r="L18" t="n">
-        <v>0.125</v>
+        <v>0.7183</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.3127</v>
+        <v>-4.2879</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.7035</v>
+        <v>-3.7427</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.6092</v>
+        <v>-0.5452</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1833</v>
+        <v>-2.1991</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9163</v>
+        <v>-2.7489</v>
       </c>
       <c r="R18" t="n">
-        <v>1.0995</v>
+        <v>0.5498</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7613</v>
+        <v>-1.0767</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1297</v>
+        <v>-1.0188</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6316000000000001</v>
+        <v>-0.0579</v>
       </c>
       <c r="V18" t="n">
-        <v>0.945</v>
+        <v>1.5889</v>
       </c>
       <c r="W18" t="n">
-        <v>1.267</v>
+        <v>2.2224</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.3219</v>
+        <v>-0.6335</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C. HORTELANO ESCRIBA</t>
+          <t>E. PINA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.747</v>
+        <v>-0.5285</v>
       </c>
       <c r="E19" t="n">
-        <v>3.885</v>
+        <v>1.3861</v>
       </c>
       <c r="F19" t="n">
-        <v>-4.6321</v>
+        <v>-1.9146</v>
       </c>
       <c r="G19" t="n">
-        <v>1.3347</v>
+        <v>-1.0514</v>
       </c>
       <c r="H19" t="n">
-        <v>1.1616</v>
+        <v>-0.5672</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1731</v>
+        <v>-0.4842</v>
       </c>
       <c r="J19" t="n">
-        <v>5.6226</v>
+        <v>1.2613</v>
       </c>
       <c r="K19" t="n">
-        <v>4.9043</v>
+        <v>1.1363</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7183</v>
+        <v>0.125</v>
       </c>
       <c r="M19" t="n">
-        <v>-4.2879</v>
+        <v>-2.3127</v>
       </c>
       <c r="N19" t="n">
-        <v>-3.7427</v>
+        <v>-1.7035</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5452</v>
+        <v>-0.6092</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.1991</v>
+        <v>0.1833</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.7489</v>
+        <v>-0.9163</v>
       </c>
       <c r="R19" t="n">
-        <v>0.5498</v>
+        <v>1.0995</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.4716</v>
+        <v>-0.6054</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.2111</v>
+        <v>-0.2259</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2604</v>
+        <v>-0.3795</v>
       </c>
       <c r="V19" t="n">
-        <v>1.5889</v>
+        <v>0.945</v>
       </c>
       <c r="W19" t="n">
-        <v>2.2224</v>
+        <v>1.267</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.6335</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.6325</v>
+        <v>-3.2115</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1103</v>
+        <v>0.1782</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.5222</v>
+        <v>-3.3897</v>
       </c>
       <c r="G20" t="n">
         <v>-1.2108</v>
@@ -2014,13 +2014,13 @@
         <v>1.0995</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.6391</v>
+        <v>-1.2181</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8258</v>
+        <v>-0.5373</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.8134</v>
+        <v>-0.6808</v>
       </c>
       <c r="V20" t="n">
         <v>-0.9658</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.6958</v>
+        <v>-3.2223</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.1901</v>
+        <v>0.0022</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.5057</v>
+        <v>-3.2245</v>
       </c>
       <c r="G21" t="n">
         <v>-2.2364</v>
@@ -2092,13 +2092,13 @@
         <v>1.4661</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.2919</v>
+        <v>-1.8184</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.3763</v>
+        <v>-1.184</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.9156</v>
+        <v>-0.6345</v>
       </c>
       <c r="V21" t="n">
         <v>-0.6335</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.4249</v>
+        <v>-4.1233</v>
       </c>
       <c r="E22" t="n">
         <v>-2.7565</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.6684</v>
+        <v>-1.3667</v>
       </c>
       <c r="G22" t="n">
         <v>-0.4351</v>
@@ -2170,13 +2170,13 @@
         <v>1.8326</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9477</v>
+        <v>-0.6461</v>
       </c>
       <c r="T22" t="n">
         <v>-0.3499</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5978</v>
+        <v>-0.2962</v>
       </c>
       <c r="V22" t="n">
         <v>0.6231</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.0129</v>
+        <v>-6.3539</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.1124</v>
+        <v>-4.3047</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.9005</v>
+        <v>-2.0491</v>
       </c>
       <c r="G23" t="n">
         <v>-4.3542</v>
@@ -2248,13 +2248,13 @@
         <v>1.0995</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.575</v>
+        <v>-0.9159</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.405</v>
+        <v>-0.5973000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.17</v>
+        <v>-0.3187</v>
       </c>
       <c r="V23" t="n">
         <v>-1.267</v>
@@ -2281,19 +2281,19 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-17.8217</v>
+        <v>-16.5398</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9521999999999986</v>
+        <v>0.9521999999999995</v>
       </c>
       <c r="F24" t="n">
-        <v>-18.7741</v>
+        <v>-17.4919</v>
       </c>
       <c r="G24" t="n">
         <v>-7.6629</v>
       </c>
       <c r="H24" t="n">
-        <v>-6.059699999999999</v>
+        <v>-6.0597</v>
       </c>
       <c r="I24" t="n">
         <v>-1.6033</v>
@@ -2305,7 +2305,7 @@
         <v>14.2262</v>
       </c>
       <c r="L24" t="n">
-        <v>0.3227000000000007</v>
+        <v>0.3227000000000002</v>
       </c>
       <c r="M24" t="n">
         <v>-22.2117</v>
@@ -2326,13 +2326,13 @@
         <v>11.9117</v>
       </c>
       <c r="S24" t="n">
-        <v>-9.894400000000001</v>
+        <v>-8.612200000000001</v>
       </c>
       <c r="T24" t="n">
         <v>-4.9621</v>
       </c>
       <c r="U24" t="n">
-        <v>-4.9323</v>
+        <v>-3.6502</v>
       </c>
       <c r="V24" t="n">
         <v>1.5681</v>
